--- a/data/screener/PIDILITIND.xlsx
+++ b/data/screener/PIDILITIND.xlsx
@@ -4054,7 +4054,7 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>1355.00</v>
+        <v>1669.00</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -4062,7 +4062,7 @@
         <v>79</v>
       </c>
       <c r="B9">
-        <v>137859.28</v>
+        <v>169869.21</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -4075,34 +4075,34 @@
         <v>38</v>
       </c>
       <c r="B16" s="16">
-        <v>42460.0</v>
+        <v>42825.0</v>
       </c>
       <c r="C16" s="16">
-        <v>42825.0</v>
+        <v>43190.0</v>
       </c>
       <c r="D16" s="16">
-        <v>43190.0</v>
+        <v>43555.0</v>
       </c>
       <c r="E16" s="16">
-        <v>43555.0</v>
+        <v>43921.0</v>
       </c>
       <c r="F16" s="16">
-        <v>43921.0</v>
+        <v>44286.0</v>
       </c>
       <c r="G16" s="16">
-        <v>44286.0</v>
+        <v>44651.0</v>
       </c>
       <c r="H16" s="16">
-        <v>44651.0</v>
+        <v>45016.0</v>
       </c>
       <c r="I16" s="16">
-        <v>45016.0</v>
+        <v>45382.0</v>
       </c>
       <c r="J16" s="16">
-        <v>45382.0</v>
+        <v>45747.0</v>
       </c>
       <c r="K16" s="16">
-        <v>45747.0</v>
+        <v>46112.0</v>
       </c>
     </row>
     <row r="17" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4110,34 +4110,34 @@
         <v>6</v>
       </c>
       <c r="B17">
-        <v>5361.17</v>
+        <v>5616.79</v>
       </c>
       <c r="C17">
-        <v>5616.79</v>
+        <v>6078.41</v>
       </c>
       <c r="D17">
-        <v>6078.41</v>
+        <v>7077.96</v>
       </c>
       <c r="E17">
-        <v>7077.96</v>
+        <v>7294.47</v>
       </c>
       <c r="F17">
-        <v>7294.47</v>
+        <v>7292.71</v>
       </c>
       <c r="G17">
-        <v>7292.71</v>
+        <v>9920.96</v>
       </c>
       <c r="H17">
-        <v>9920.96</v>
+        <v>11799.1</v>
       </c>
       <c r="I17">
-        <v>11799.1</v>
+        <v>12382.99</v>
       </c>
       <c r="J17">
-        <v>12382.99</v>
+        <v>13140.31</v>
       </c>
       <c r="K17">
-        <v>13140.31</v>
+        <v>14600.83</v>
       </c>
     </row>
     <row r="18" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4145,34 +4145,34 @@
         <v>80</v>
       </c>
       <c r="B18">
-        <v>2561.41</v>
+        <v>2670.29</v>
       </c>
       <c r="C18">
-        <v>2670.29</v>
+        <v>2883.88</v>
       </c>
       <c r="D18">
-        <v>2883.88</v>
+        <v>3661.79</v>
       </c>
       <c r="E18">
-        <v>3661.79</v>
+        <v>3381.28</v>
       </c>
       <c r="F18">
-        <v>3381.28</v>
+        <v>3494.99</v>
       </c>
       <c r="G18">
-        <v>3494.99</v>
+        <v>5689.14</v>
       </c>
       <c r="H18">
-        <v>5689.14</v>
+        <v>6821.12</v>
       </c>
       <c r="I18">
-        <v>6821.12</v>
+        <v>5867.9</v>
       </c>
       <c r="J18">
-        <v>5867.9</v>
+        <v>6135.04</v>
       </c>
       <c r="K18">
-        <v>6135.04</v>
+        <v>6519.35</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4180,34 +4180,34 @@
         <v>81</v>
       </c>
       <c r="B19">
-        <v>-23.27</v>
+        <v>30.73</v>
       </c>
       <c r="C19">
-        <v>30.73</v>
+        <v>-3.77</v>
       </c>
       <c r="D19">
-        <v>-3.77</v>
+        <v>75.21</v>
       </c>
       <c r="E19">
-        <v>75.21</v>
+        <v>-21.22</v>
       </c>
       <c r="F19">
-        <v>-21.22</v>
+        <v>118.32</v>
       </c>
       <c r="G19">
-        <v>118.32</v>
+        <v>244.96</v>
       </c>
       <c r="H19">
-        <v>244.96</v>
+        <v>61.72</v>
       </c>
       <c r="I19">
-        <v>61.72</v>
+        <v>-126.12</v>
       </c>
       <c r="J19">
-        <v>-126.12</v>
+        <v>138.76</v>
       </c>
       <c r="K19">
-        <v>138.76</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="20" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4215,34 +4215,34 @@
         <v>82</v>
       </c>
       <c r="B20">
-        <v>48.97</v>
+        <v>53.21</v>
       </c>
       <c r="C20">
-        <v>53.21</v>
+        <v>59.16</v>
       </c>
       <c r="D20">
-        <v>59.16</v>
+        <v>66.43</v>
       </c>
       <c r="E20">
-        <v>66.43</v>
+        <v>67.19</v>
       </c>
       <c r="F20">
-        <v>67.19</v>
+        <v>68.66</v>
       </c>
       <c r="G20">
-        <v>68.66</v>
+        <v>87.89</v>
       </c>
       <c r="H20">
-        <v>87.89</v>
+        <v>97.04</v>
       </c>
       <c r="I20">
-        <v>97.04</v>
+        <v>106.92</v>
       </c>
       <c r="J20">
-        <v>106.92</v>
+        <v>113.15</v>
       </c>
       <c r="K20">
-        <v>113.15</v>
+        <v>104.16</v>
       </c>
     </row>
     <row r="21" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4250,34 +4250,34 @@
         <v>83</v>
       </c>
       <c r="B21">
-        <v>345.8</v>
+        <v>56.83</v>
       </c>
       <c r="C21">
-        <v>56.83</v>
+        <v>109.42</v>
       </c>
       <c r="D21">
-        <v>109.42</v>
+        <v>122.97</v>
       </c>
       <c r="E21">
-        <v>122.97</v>
+        <v>153.27</v>
       </c>
       <c r="F21">
-        <v>153.27</v>
+        <v>226.5</v>
       </c>
       <c r="G21">
-        <v>226.5</v>
+        <v>299.49</v>
       </c>
       <c r="H21">
-        <v>299.49</v>
+        <v>329.87</v>
       </c>
       <c r="I21">
-        <v>329.87</v>
+        <v>412.83</v>
       </c>
       <c r="J21">
-        <v>412.83</v>
+        <v>557.64</v>
       </c>
       <c r="K21">
-        <v>472.32</v>
+        <v>621.89</v>
       </c>
     </row>
     <row r="22" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4285,34 +4285,34 @@
         <v>84</v>
       </c>
       <c r="B22">
-        <v>572.46</v>
+        <v>645.62</v>
       </c>
       <c r="C22">
-        <v>645.62</v>
+        <v>712.88</v>
       </c>
       <c r="D22">
-        <v>712.88</v>
+        <v>837.13</v>
       </c>
       <c r="E22">
-        <v>837.13</v>
+        <v>927.66</v>
       </c>
       <c r="F22">
-        <v>927.66</v>
+        <v>981.91</v>
       </c>
       <c r="G22">
-        <v>981.91</v>
+        <v>1113.24</v>
       </c>
       <c r="H22">
-        <v>1113.24</v>
+        <v>1246.25</v>
       </c>
       <c r="I22">
-        <v>1246.25</v>
+        <v>1465.97</v>
       </c>
       <c r="J22">
-        <v>1465.97</v>
+        <v>1742.45</v>
       </c>
       <c r="K22">
-        <v>1742.45</v>
+        <v>1942.25</v>
       </c>
     </row>
     <row r="23" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4320,34 +4320,34 @@
         <v>85</v>
       </c>
       <c r="B23">
-        <v>434.86</v>
+        <v>736.4</v>
       </c>
       <c r="C23">
-        <v>736.4</v>
+        <v>766.29</v>
       </c>
       <c r="D23">
-        <v>766.29</v>
+        <v>845.9</v>
       </c>
       <c r="E23">
-        <v>845.9</v>
+        <v>905.14</v>
       </c>
       <c r="F23">
-        <v>905.14</v>
+        <v>769.96</v>
       </c>
       <c r="G23">
-        <v>769.96</v>
+        <v>908.39</v>
       </c>
       <c r="H23">
-        <v>908.39</v>
+        <v>1142.26</v>
       </c>
       <c r="I23">
-        <v>1142.26</v>
+        <v>1460.42</v>
       </c>
       <c r="J23">
-        <v>1460.42</v>
+        <v>1534.17</v>
       </c>
       <c r="K23">
-        <v>1534.17</v>
+        <v>1701.17</v>
       </c>
     </row>
     <row r="24" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4355,34 +4355,34 @@
         <v>86</v>
       </c>
       <c r="B24">
-        <v>200.92</v>
+        <v>223.28</v>
       </c>
       <c r="C24">
-        <v>223.28</v>
+        <v>201.79</v>
       </c>
       <c r="D24">
-        <v>201.79</v>
+        <v>248.31</v>
       </c>
       <c r="E24">
-        <v>248.31</v>
+        <v>262.69</v>
       </c>
       <c r="F24">
-        <v>262.69</v>
+        <v>182.66</v>
       </c>
       <c r="G24">
-        <v>182.66</v>
+        <v>211.36</v>
       </c>
       <c r="H24">
-        <v>211.36</v>
+        <v>238.19</v>
       </c>
       <c r="I24">
-        <v>238.19</v>
+        <v>234.38</v>
       </c>
       <c r="J24">
-        <v>234.38</v>
+        <v>186.04</v>
       </c>
       <c r="K24">
-        <v>271.36</v>
+        <v>221.01</v>
       </c>
     </row>
     <row r="25" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4390,34 +4390,34 @@
         <v>9</v>
       </c>
       <c r="B25">
-        <v>81.03</v>
+        <v>115.45</v>
       </c>
       <c r="C25">
-        <v>115.45</v>
+        <v>153.0</v>
       </c>
       <c r="D25">
-        <v>153.0</v>
+        <v>129.79</v>
       </c>
       <c r="E25">
-        <v>129.79</v>
+        <v>97.27</v>
       </c>
       <c r="F25">
-        <v>97.27</v>
+        <v>74.03</v>
       </c>
       <c r="G25">
-        <v>74.03</v>
+        <v>39.06</v>
       </c>
       <c r="H25">
-        <v>39.06</v>
+        <v>54.53</v>
       </c>
       <c r="I25">
-        <v>54.53</v>
+        <v>62.75</v>
       </c>
       <c r="J25">
-        <v>62.75</v>
+        <v>220.95</v>
       </c>
       <c r="K25">
-        <v>220.95</v>
+        <v>247.8</v>
       </c>
     </row>
     <row r="26" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4425,34 +4425,34 @@
         <v>10</v>
       </c>
       <c r="B26">
-        <v>100.47</v>
+        <v>115.14</v>
       </c>
       <c r="C26">
-        <v>115.14</v>
+        <v>119.88</v>
       </c>
       <c r="D26">
-        <v>119.88</v>
+        <v>132.74</v>
       </c>
       <c r="E26">
-        <v>132.74</v>
+        <v>169.92</v>
       </c>
       <c r="F26">
-        <v>169.92</v>
+        <v>200.66</v>
       </c>
       <c r="G26">
-        <v>200.66</v>
+        <v>239.61</v>
       </c>
       <c r="H26">
-        <v>239.61</v>
+        <v>269.74</v>
       </c>
       <c r="I26">
-        <v>269.74</v>
+        <v>340.66</v>
       </c>
       <c r="J26">
-        <v>340.66</v>
+        <v>358.48</v>
       </c>
       <c r="K26">
-        <v>358.48</v>
+        <v>394.71</v>
       </c>
     </row>
     <row r="27" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4460,34 +4460,34 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>13.27</v>
+        <v>13.93</v>
       </c>
       <c r="C27">
-        <v>13.93</v>
+        <v>15.54</v>
       </c>
       <c r="D27">
-        <v>15.54</v>
+        <v>26.07</v>
       </c>
       <c r="E27">
-        <v>26.07</v>
+        <v>33.6</v>
       </c>
       <c r="F27">
-        <v>33.6</v>
+        <v>37.23</v>
       </c>
       <c r="G27">
-        <v>37.23</v>
+        <v>42.08</v>
       </c>
       <c r="H27">
-        <v>42.08</v>
+        <v>47.64</v>
       </c>
       <c r="I27">
-        <v>47.64</v>
+        <v>51.19</v>
       </c>
       <c r="J27">
-        <v>51.19</v>
+        <v>50.35</v>
       </c>
       <c r="K27">
-        <v>50.35</v>
+        <v>54.22</v>
       </c>
     </row>
     <row r="28" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4495,34 +4495,34 @@
         <v>12</v>
       </c>
       <c r="B28">
-        <v>1140.77</v>
+        <v>1248.27</v>
       </c>
       <c r="C28">
-        <v>1248.27</v>
+        <v>1358.8</v>
       </c>
       <c r="D28">
-        <v>1358.8</v>
+        <v>1341.62</v>
       </c>
       <c r="E28">
-        <v>1341.62</v>
+        <v>1469.77</v>
       </c>
       <c r="F28">
-        <v>1469.77</v>
+        <v>1522.49</v>
       </c>
       <c r="G28">
-        <v>1522.49</v>
+        <v>1613.78</v>
       </c>
       <c r="H28">
-        <v>1613.78</v>
+        <v>1723.24</v>
       </c>
       <c r="I28">
-        <v>1723.24</v>
+        <v>2379.35</v>
       </c>
       <c r="J28">
-        <v>2379.35</v>
+        <v>2822.7</v>
       </c>
       <c r="K28">
-        <v>2822.7</v>
+        <v>3320.17</v>
       </c>
     </row>
     <row r="29" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4530,34 +4530,34 @@
         <v>13</v>
       </c>
       <c r="B29">
-        <v>333.54</v>
+        <v>385.05</v>
       </c>
       <c r="C29">
-        <v>385.05</v>
+        <v>392.71</v>
       </c>
       <c r="D29">
-        <v>392.71</v>
+        <v>413.23</v>
       </c>
       <c r="E29">
-        <v>413.23</v>
+        <v>347.72</v>
       </c>
       <c r="F29">
-        <v>347.72</v>
+        <v>396.36</v>
       </c>
       <c r="G29">
-        <v>396.36</v>
+        <v>407.02</v>
       </c>
       <c r="H29">
-        <v>407.02</v>
+        <v>434.37</v>
       </c>
       <c r="I29">
-        <v>434.37</v>
+        <v>631.93</v>
       </c>
       <c r="J29">
-        <v>631.93</v>
+        <v>726.53</v>
       </c>
       <c r="K29">
-        <v>726.53</v>
+        <v>849.45</v>
       </c>
     </row>
     <row r="30" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4565,34 +4565,34 @@
         <v>14</v>
       </c>
       <c r="B30">
-        <v>802.83</v>
+        <v>859.99</v>
       </c>
       <c r="C30">
-        <v>859.99</v>
+        <v>962.35</v>
       </c>
       <c r="D30">
-        <v>962.35</v>
+        <v>924.91</v>
       </c>
       <c r="E30">
-        <v>924.91</v>
+        <v>1116.42</v>
       </c>
       <c r="F30">
-        <v>1116.42</v>
+        <v>1131.21</v>
       </c>
       <c r="G30">
-        <v>1131.21</v>
+        <v>1207.56</v>
       </c>
       <c r="H30">
-        <v>1207.56</v>
+        <v>1273.25</v>
       </c>
       <c r="I30">
-        <v>1273.25</v>
+        <v>1729.38</v>
       </c>
       <c r="J30">
-        <v>1729.38</v>
+        <v>2076.24</v>
       </c>
       <c r="K30">
-        <v>2076.24</v>
+        <v>2448.92</v>
       </c>
     </row>
     <row r="31" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4600,34 +4600,34 @@
         <v>70</v>
       </c>
       <c r="B31">
-        <v>212.77</v>
+        <v>243.53</v>
       </c>
       <c r="C31">
-        <v>243.53</v>
+        <v>304.68</v>
       </c>
       <c r="D31">
-        <v>304.68</v>
+        <v>330.2</v>
       </c>
       <c r="E31">
-        <v>330.2</v>
+        <v>355.67</v>
       </c>
       <c r="F31">
-        <v>355.67</v>
+        <v>431.97</v>
       </c>
       <c r="G31">
-        <v>431.97</v>
+        <v>508.3</v>
       </c>
       <c r="H31">
-        <v>508.3</v>
+        <v>559.13</v>
       </c>
       <c r="I31">
-        <v>559.13</v>
+        <v>813.76</v>
       </c>
       <c r="J31">
-        <v>813.76</v>
+        <v>1017.2</v>
       </c>
       <c r="K31">
-        <v>1017.2</v>
+        <v>1170.47</v>
       </c>
     </row>
     <row r="32" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -4662,34 +4662,34 @@
         <v>38</v>
       </c>
       <c r="B41" s="16">
-        <v>45199.0</v>
+        <v>45382.0</v>
       </c>
       <c r="C41" s="16">
-        <v>45291.0</v>
+        <v>45473.0</v>
       </c>
       <c r="D41" s="16">
-        <v>45382.0</v>
+        <v>45565.0</v>
       </c>
       <c r="E41" s="16">
-        <v>45473.0</v>
+        <v>45657.0</v>
       </c>
       <c r="F41" s="16">
-        <v>45565.0</v>
+        <v>45747.0</v>
       </c>
       <c r="G41" s="16">
-        <v>45657.0</v>
+        <v>45838.0</v>
       </c>
       <c r="H41" s="16">
-        <v>45747.0</v>
+        <v>45930.0</v>
       </c>
       <c r="I41" s="16">
-        <v>45838.0</v>
+        <v>46022.0</v>
       </c>
       <c r="J41" s="16">
-        <v>45930.0</v>
+        <v>46112.0</v>
       </c>
       <c r="K41" s="16">
-        <v>46022.0</v>
+        <v>46203.0</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4697,34 +4697,34 @@
         <v>6</v>
       </c>
       <c r="B42">
-        <v>3076.04</v>
+        <v>2901.85</v>
       </c>
       <c r="C42">
-        <v>3129.99</v>
+        <v>3395.35</v>
       </c>
       <c r="D42">
-        <v>2901.85</v>
+        <v>3234.91</v>
       </c>
       <c r="E42">
-        <v>3395.35</v>
+        <v>3368.91</v>
       </c>
       <c r="F42">
-        <v>3234.91</v>
+        <v>3141.14</v>
       </c>
       <c r="G42">
-        <v>3368.91</v>
+        <v>3753.1</v>
       </c>
       <c r="H42">
-        <v>3141.14</v>
+        <v>3554.44</v>
       </c>
       <c r="I42">
-        <v>3753.1</v>
+        <v>3709.91</v>
       </c>
       <c r="J42">
-        <v>3554.44</v>
+        <v>3583.38</v>
       </c>
       <c r="K42">
-        <v>3709.91</v>
+        <v>4551.55</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4732,34 +4732,34 @@
         <v>7</v>
       </c>
       <c r="B43">
-        <v>2397.68</v>
+        <v>2326.91</v>
       </c>
       <c r="C43">
-        <v>2387.54</v>
+        <v>2583.42</v>
       </c>
       <c r="D43">
-        <v>2326.91</v>
+        <v>2467.32</v>
       </c>
       <c r="E43">
-        <v>2583.42</v>
+        <v>2570.98</v>
       </c>
       <c r="F43">
-        <v>2467.32</v>
+        <v>2509.36</v>
       </c>
       <c r="G43">
-        <v>2570.98</v>
+        <v>2812.12</v>
       </c>
       <c r="H43">
-        <v>2509.36</v>
+        <v>2704.06</v>
       </c>
       <c r="I43">
-        <v>2812.12</v>
+        <v>2815.7</v>
       </c>
       <c r="J43">
-        <v>2704.06</v>
+        <v>2752.55</v>
       </c>
       <c r="K43">
-        <v>2815.7</v>
+        <v>3357.66</v>
       </c>
     </row>
     <row r="44" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4767,34 +4767,34 @@
         <v>9</v>
       </c>
       <c r="B44">
-        <v>31.59</v>
+        <v>-22.79</v>
       </c>
       <c r="C44">
-        <v>37.22</v>
+        <v>53.94</v>
       </c>
       <c r="D44">
-        <v>-22.79</v>
+        <v>57.12</v>
       </c>
       <c r="E44">
-        <v>53.94</v>
+        <v>55.78</v>
       </c>
       <c r="F44">
-        <v>57.12</v>
+        <v>55.46</v>
       </c>
       <c r="G44">
-        <v>55.78</v>
+        <v>85.94</v>
       </c>
       <c r="H44">
-        <v>55.46</v>
+        <v>50.16</v>
       </c>
       <c r="I44">
-        <v>85.94</v>
+        <v>59.8</v>
       </c>
       <c r="J44">
-        <v>50.16</v>
+        <v>56.8</v>
       </c>
       <c r="K44">
-        <v>59.8</v>
+        <v>108.73</v>
       </c>
     </row>
     <row r="45" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4802,34 +4802,34 @@
         <v>10</v>
       </c>
       <c r="B45">
-        <v>75.21</v>
+        <v>112.53</v>
       </c>
       <c r="C45">
-        <v>79.49</v>
+        <v>84.42</v>
       </c>
       <c r="D45">
-        <v>112.53</v>
+        <v>87.88</v>
       </c>
       <c r="E45">
-        <v>84.42</v>
+        <v>89.5</v>
       </c>
       <c r="F45">
-        <v>87.88</v>
+        <v>96.68</v>
       </c>
       <c r="G45">
-        <v>89.5</v>
+        <v>96.68</v>
       </c>
       <c r="H45">
-        <v>96.68</v>
+        <v>99.95</v>
       </c>
       <c r="I45">
-        <v>96.68</v>
+        <v>100.99</v>
       </c>
       <c r="J45">
-        <v>99.95</v>
+        <v>97.09</v>
       </c>
       <c r="K45">
-        <v>100.99</v>
+        <v>97.29</v>
       </c>
     </row>
     <row r="46" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4837,34 +4837,34 @@
         <v>11</v>
       </c>
       <c r="B46">
-        <v>13.13</v>
+        <v>13.42</v>
       </c>
       <c r="C46">
-        <v>12.76</v>
+        <v>11.82</v>
       </c>
       <c r="D46">
-        <v>13.42</v>
+        <v>11.73</v>
       </c>
       <c r="E46">
-        <v>11.82</v>
+        <v>12.45</v>
       </c>
       <c r="F46">
-        <v>11.73</v>
+        <v>14.35</v>
       </c>
       <c r="G46">
-        <v>12.45</v>
+        <v>13.77</v>
       </c>
       <c r="H46">
-        <v>14.35</v>
+        <v>13.28</v>
       </c>
       <c r="I46">
-        <v>13.77</v>
+        <v>13.28</v>
       </c>
       <c r="J46">
-        <v>13.28</v>
+        <v>13.89</v>
       </c>
       <c r="K46">
-        <v>13.28</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="47" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4872,34 +4872,34 @@
         <v>12</v>
       </c>
       <c r="B47">
-        <v>621.61</v>
+        <v>426.2</v>
       </c>
       <c r="C47">
-        <v>687.42</v>
+        <v>769.63</v>
       </c>
       <c r="D47">
-        <v>426.2</v>
+        <v>725.1</v>
       </c>
       <c r="E47">
-        <v>769.63</v>
+        <v>751.76</v>
       </c>
       <c r="F47">
-        <v>725.1</v>
+        <v>576.21</v>
       </c>
       <c r="G47">
-        <v>751.76</v>
+        <v>916.47</v>
       </c>
       <c r="H47">
-        <v>576.21</v>
+        <v>787.31</v>
       </c>
       <c r="I47">
-        <v>916.47</v>
+        <v>839.74</v>
       </c>
       <c r="J47">
-        <v>787.31</v>
+        <v>776.65</v>
       </c>
       <c r="K47">
-        <v>839.74</v>
+        <v>1191.99</v>
       </c>
     </row>
     <row r="48" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4907,34 +4907,34 @@
         <v>13</v>
       </c>
       <c r="B48">
-        <v>163.08</v>
+        <v>121.91</v>
       </c>
       <c r="C48">
-        <v>176.5</v>
+        <v>198.36</v>
       </c>
       <c r="D48">
-        <v>121.91</v>
+        <v>184.8</v>
       </c>
       <c r="E48">
-        <v>198.36</v>
+        <v>194.68</v>
       </c>
       <c r="F48">
-        <v>184.8</v>
+        <v>148.69</v>
       </c>
       <c r="G48">
-        <v>194.68</v>
+        <v>238.34</v>
       </c>
       <c r="H48">
-        <v>148.69</v>
+        <v>202.71</v>
       </c>
       <c r="I48">
-        <v>238.34</v>
+        <v>215.9</v>
       </c>
       <c r="J48">
-        <v>202.71</v>
+        <v>192.5</v>
       </c>
       <c r="K48">
-        <v>215.9</v>
+        <v>308.48</v>
       </c>
     </row>
     <row r="49" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -4942,34 +4942,34 @@
         <v>14</v>
       </c>
       <c r="B49">
-        <v>450.15</v>
+        <v>300.6</v>
       </c>
       <c r="C49">
-        <v>510.48</v>
+        <v>566.92</v>
       </c>
       <c r="D49">
-        <v>300.6</v>
+        <v>534.56</v>
       </c>
       <c r="E49">
-        <v>566.92</v>
+        <v>552.42</v>
       </c>
       <c r="F49">
-        <v>534.56</v>
+        <v>422.34</v>
       </c>
       <c r="G49">
-        <v>552.42</v>
+        <v>672.41</v>
       </c>
       <c r="H49">
-        <v>422.34</v>
+        <v>579.23</v>
       </c>
       <c r="I49">
-        <v>672.41</v>
+        <v>618.01</v>
       </c>
       <c r="J49">
-        <v>579.23</v>
+        <v>579.27</v>
       </c>
       <c r="K49">
-        <v>618.01</v>
+        <v>872.41</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
@@ -4977,34 +4977,34 @@
         <v>8</v>
       </c>
       <c r="B50">
-        <v>678.36</v>
+        <v>574.94</v>
       </c>
       <c r="C50">
-        <v>742.45</v>
+        <v>811.93</v>
       </c>
       <c r="D50">
-        <v>574.94</v>
+        <v>767.59</v>
       </c>
       <c r="E50">
-        <v>811.93</v>
+        <v>797.93</v>
       </c>
       <c r="F50">
-        <v>767.59</v>
+        <v>631.78</v>
       </c>
       <c r="G50">
-        <v>797.93</v>
+        <v>940.98</v>
       </c>
       <c r="H50">
-        <v>631.78</v>
+        <v>850.38</v>
       </c>
       <c r="I50">
-        <v>940.98</v>
+        <v>894.21</v>
       </c>
       <c r="J50">
-        <v>850.38</v>
+        <v>830.83</v>
       </c>
       <c r="K50">
-        <v>894.21</v>
+        <v>1193.89</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
@@ -5029,34 +5029,34 @@
         <v>38</v>
       </c>
       <c r="B56" s="16">
-        <v>42460.0</v>
+        <v>42825.0</v>
       </c>
       <c r="C56" s="16">
-        <v>42825.0</v>
+        <v>43190.0</v>
       </c>
       <c r="D56" s="16">
-        <v>43190.0</v>
+        <v>43555.0</v>
       </c>
       <c r="E56" s="16">
-        <v>43555.0</v>
+        <v>43921.0</v>
       </c>
       <c r="F56" s="16">
-        <v>43921.0</v>
+        <v>44286.0</v>
       </c>
       <c r="G56" s="16">
-        <v>44286.0</v>
+        <v>44651.0</v>
       </c>
       <c r="H56" s="16">
-        <v>44651.0</v>
+        <v>45016.0</v>
       </c>
       <c r="I56" s="16">
-        <v>45016.0</v>
+        <v>45382.0</v>
       </c>
       <c r="J56" s="16">
-        <v>45382.0</v>
+        <v>45747.0</v>
       </c>
       <c r="K56" s="16">
-        <v>45747.0</v>
+        <v>46112.0</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
@@ -5067,31 +5067,31 @@
         <v>51.27</v>
       </c>
       <c r="C57">
-        <v>51.27</v>
+        <v>50.78</v>
       </c>
       <c r="D57">
-        <v>50.78</v>
+        <v>50.8</v>
       </c>
       <c r="E57">
-        <v>50.8</v>
+        <v>50.81</v>
       </c>
       <c r="F57">
-        <v>50.81</v>
+        <v>50.82</v>
       </c>
       <c r="G57">
-        <v>50.82</v>
+        <v>50.83</v>
       </c>
       <c r="H57">
         <v>50.83</v>
       </c>
       <c r="I57">
-        <v>50.83</v>
+        <v>50.86</v>
       </c>
       <c r="J57">
         <v>50.86</v>
       </c>
       <c r="K57">
-        <v>50.86</v>
+        <v>101.78</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
@@ -5099,34 +5099,34 @@
         <v>25</v>
       </c>
       <c r="B58">
-        <v>2586.72</v>
+        <v>3419.64</v>
       </c>
       <c r="C58">
-        <v>3419.64</v>
+        <v>3523.26</v>
       </c>
       <c r="D58">
-        <v>3523.26</v>
+        <v>4097.29</v>
       </c>
       <c r="E58">
-        <v>4097.29</v>
+        <v>4404.8</v>
       </c>
       <c r="F58">
-        <v>4404.8</v>
+        <v>5542.14</v>
       </c>
       <c r="G58">
-        <v>5542.14</v>
+        <v>6352.88</v>
       </c>
       <c r="H58">
-        <v>6352.88</v>
+        <v>7161.45</v>
       </c>
       <c r="I58">
-        <v>7161.45</v>
+        <v>8356.3</v>
       </c>
       <c r="J58">
-        <v>8356.3</v>
+        <v>9703.6</v>
       </c>
       <c r="K58">
-        <v>9703.6</v>
+        <v>10730.39</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
@@ -5134,34 +5134,34 @@
         <v>71</v>
       </c>
       <c r="B59">
-        <v>80.02</v>
+        <v>97.51</v>
       </c>
       <c r="C59">
-        <v>97.51</v>
+        <v>124.57</v>
       </c>
       <c r="D59">
-        <v>124.57</v>
+        <v>112.74</v>
       </c>
       <c r="E59">
-        <v>112.74</v>
+        <v>287.69</v>
       </c>
       <c r="F59">
-        <v>287.69</v>
+        <v>331.0</v>
       </c>
       <c r="G59">
-        <v>331.0</v>
+        <v>415.83</v>
       </c>
       <c r="H59">
-        <v>415.83</v>
+        <v>390.61</v>
       </c>
       <c r="I59">
-        <v>390.61</v>
+        <v>382.47</v>
       </c>
       <c r="J59">
-        <v>382.47</v>
+        <v>454.14</v>
       </c>
       <c r="K59">
-        <v>454.14</v>
+        <v>417.21</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
@@ -5169,34 +5169,34 @@
         <v>72</v>
       </c>
       <c r="B60">
-        <v>995.87</v>
+        <v>1202.01</v>
       </c>
       <c r="C60">
-        <v>1202.01</v>
+        <v>1499.99</v>
       </c>
       <c r="D60">
-        <v>1499.99</v>
+        <v>1642.96</v>
       </c>
       <c r="E60">
-        <v>1642.96</v>
+        <v>1779.4</v>
       </c>
       <c r="F60">
-        <v>1779.4</v>
+        <v>2889.87</v>
       </c>
       <c r="G60">
-        <v>2889.87</v>
+        <v>2674.8</v>
       </c>
       <c r="H60">
-        <v>2674.8</v>
+        <v>2901.98</v>
       </c>
       <c r="I60">
-        <v>2901.98</v>
+        <v>3285.98</v>
       </c>
       <c r="J60">
-        <v>3285.98</v>
+        <v>3775.09</v>
       </c>
       <c r="K60">
-        <v>3775.09</v>
+        <v>4149.48</v>
       </c>
     </row>
     <row r="61" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5204,34 +5204,34 @@
         <v>26</v>
       </c>
       <c r="B61">
-        <v>3713.88</v>
+        <v>4770.43</v>
       </c>
       <c r="C61">
-        <v>4770.43</v>
+        <v>5198.6</v>
       </c>
       <c r="D61">
-        <v>5198.6</v>
+        <v>5903.79</v>
       </c>
       <c r="E61">
-        <v>5903.79</v>
+        <v>6522.7</v>
       </c>
       <c r="F61">
-        <v>6522.7</v>
+        <v>8813.83</v>
       </c>
       <c r="G61">
-        <v>8813.83</v>
+        <v>9494.34</v>
       </c>
       <c r="H61">
-        <v>9494.34</v>
+        <v>10504.87</v>
       </c>
       <c r="I61">
-        <v>10504.87</v>
+        <v>12075.61</v>
       </c>
       <c r="J61">
-        <v>12075.61</v>
+        <v>13983.69</v>
       </c>
       <c r="K61">
-        <v>13983.69</v>
+        <v>15398.86</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
@@ -5239,34 +5239,34 @@
         <v>27</v>
       </c>
       <c r="B62">
-        <v>1137.46</v>
+        <v>1275.25</v>
       </c>
       <c r="C62">
-        <v>1275.25</v>
+        <v>1342.19</v>
       </c>
       <c r="D62">
-        <v>1342.19</v>
+        <v>1447.61</v>
       </c>
       <c r="E62">
-        <v>1447.61</v>
+        <v>1806.71</v>
       </c>
       <c r="F62">
-        <v>1806.71</v>
+        <v>4417.92</v>
       </c>
       <c r="G62">
-        <v>4417.92</v>
+        <v>4703.26</v>
       </c>
       <c r="H62">
-        <v>4703.26</v>
+        <v>4914.08</v>
       </c>
       <c r="I62">
-        <v>4914.08</v>
+        <v>5450.63</v>
       </c>
       <c r="J62">
-        <v>5450.63</v>
+        <v>5705.29</v>
       </c>
       <c r="K62">
-        <v>5705.29</v>
+        <v>5773.63</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
@@ -5274,34 +5274,34 @@
         <v>28</v>
       </c>
       <c r="B63">
-        <v>158.07</v>
+        <v>147.71</v>
       </c>
       <c r="C63">
-        <v>147.71</v>
+        <v>227.73</v>
       </c>
       <c r="D63">
-        <v>227.73</v>
+        <v>242.13</v>
       </c>
       <c r="E63">
-        <v>242.13</v>
+        <v>259.33</v>
       </c>
       <c r="F63">
-        <v>259.33</v>
+        <v>293.87</v>
       </c>
       <c r="G63">
-        <v>293.87</v>
+        <v>225.42</v>
       </c>
       <c r="H63">
-        <v>225.42</v>
+        <v>405.94</v>
       </c>
       <c r="I63">
-        <v>405.94</v>
+        <v>148.09</v>
       </c>
       <c r="J63">
-        <v>148.09</v>
+        <v>128.95</v>
       </c>
       <c r="K63">
-        <v>128.95</v>
+        <v>328.87</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
@@ -5309,34 +5309,34 @@
         <v>29</v>
       </c>
       <c r="B64">
-        <v>705.54</v>
+        <v>1443.1</v>
       </c>
       <c r="C64">
-        <v>1443.1</v>
+        <v>1245.94</v>
       </c>
       <c r="D64">
-        <v>1245.94</v>
+        <v>1547.7</v>
       </c>
       <c r="E64">
-        <v>1547.7</v>
+        <v>1186.19</v>
       </c>
       <c r="F64">
-        <v>1186.19</v>
+        <v>515.97</v>
       </c>
       <c r="G64">
-        <v>515.97</v>
+        <v>458.61</v>
       </c>
       <c r="H64">
-        <v>458.61</v>
+        <v>880.85</v>
       </c>
       <c r="I64">
-        <v>880.85</v>
+        <v>2235.04</v>
       </c>
       <c r="J64">
-        <v>2235.04</v>
+        <v>3551.32</v>
       </c>
       <c r="K64">
-        <v>3551.32</v>
+        <v>4349.61</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.2">
@@ -5344,34 +5344,34 @@
         <v>73</v>
       </c>
       <c r="B65">
-        <v>1712.81</v>
+        <v>1904.37</v>
       </c>
       <c r="C65">
-        <v>1904.37</v>
+        <v>2382.74</v>
       </c>
       <c r="D65">
-        <v>2382.74</v>
+        <v>2666.35</v>
       </c>
       <c r="E65">
-        <v>2666.35</v>
+        <v>3270.47</v>
       </c>
       <c r="F65">
-        <v>3270.47</v>
+        <v>3586.07</v>
       </c>
       <c r="G65">
-        <v>3586.07</v>
+        <v>4107.05</v>
       </c>
       <c r="H65">
-        <v>4107.05</v>
+        <v>4304.0</v>
       </c>
       <c r="I65">
-        <v>4304.0</v>
+        <v>4241.85</v>
       </c>
       <c r="J65">
-        <v>4241.85</v>
+        <v>4598.13</v>
       </c>
       <c r="K65">
-        <v>4598.13</v>
+        <v>4946.75</v>
       </c>
     </row>
     <row r="66" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5379,34 +5379,34 @@
         <v>26</v>
       </c>
       <c r="B66">
-        <v>3713.88</v>
+        <v>4770.43</v>
       </c>
       <c r="C66">
-        <v>4770.43</v>
+        <v>5198.6</v>
       </c>
       <c r="D66">
-        <v>5198.6</v>
+        <v>5903.79</v>
       </c>
       <c r="E66">
-        <v>5903.79</v>
+        <v>6522.7</v>
       </c>
       <c r="F66">
-        <v>6522.7</v>
+        <v>8813.83</v>
       </c>
       <c r="G66">
-        <v>8813.83</v>
+        <v>9494.34</v>
       </c>
       <c r="H66">
-        <v>9494.34</v>
+        <v>10504.87</v>
       </c>
       <c r="I66">
-        <v>10504.87</v>
+        <v>12075.61</v>
       </c>
       <c r="J66">
-        <v>12075.61</v>
+        <v>13983.69</v>
       </c>
       <c r="K66">
-        <v>13983.69</v>
+        <v>15398.86</v>
       </c>
     </row>
     <row r="67" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -5414,34 +5414,34 @@
         <v>78</v>
       </c>
       <c r="B67">
-        <v>701.59</v>
+        <v>768.54</v>
       </c>
       <c r="C67">
-        <v>768.54</v>
+        <v>938.13</v>
       </c>
       <c r="D67">
-        <v>938.13</v>
+        <v>1056.01</v>
       </c>
       <c r="E67">
-        <v>1056.01</v>
+        <v>1088.5</v>
       </c>
       <c r="F67">
-        <v>1088.5</v>
+        <v>1321.02</v>
       </c>
       <c r="G67">
-        <v>1321.02</v>
+        <v>1430.54</v>
       </c>
       <c r="H67">
-        <v>1430.54</v>
+        <v>1535.27</v>
       </c>
       <c r="I67">
-        <v>1535.27</v>
+        <v>1674.69</v>
       </c>
       <c r="J67">
-        <v>1674.69</v>
+        <v>1811.15</v>
       </c>
       <c r="K67">
-        <v>1811.15</v>
+        <v>2181.1</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
@@ -5449,34 +5449,34 @@
         <v>45</v>
       </c>
       <c r="B68">
-        <v>627.43</v>
+        <v>720.86</v>
       </c>
       <c r="C68">
-        <v>720.86</v>
+        <v>804.33</v>
       </c>
       <c r="D68">
-        <v>804.33</v>
+        <v>934.45</v>
       </c>
       <c r="E68">
-        <v>934.45</v>
+        <v>929.47</v>
       </c>
       <c r="F68">
-        <v>929.47</v>
+        <v>1234.15</v>
       </c>
       <c r="G68">
-        <v>1234.15</v>
+        <v>1695.09</v>
       </c>
       <c r="H68">
-        <v>1695.09</v>
+        <v>1817.08</v>
       </c>
       <c r="I68">
-        <v>1817.08</v>
+        <v>1414.9</v>
       </c>
       <c r="J68">
-        <v>1414.9</v>
+        <v>1685.09</v>
       </c>
       <c r="K68">
-        <v>1685.09</v>
+        <v>1737.6</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
@@ -5484,34 +5484,34 @@
         <v>87</v>
       </c>
       <c r="B69">
-        <v>131.76</v>
+        <v>99.94</v>
       </c>
       <c r="C69">
-        <v>99.94</v>
+        <v>163.58</v>
       </c>
       <c r="D69">
-        <v>163.58</v>
+        <v>190.43</v>
       </c>
       <c r="E69">
-        <v>190.43</v>
+        <v>703.25</v>
       </c>
       <c r="F69">
-        <v>703.25</v>
+        <v>451.46</v>
       </c>
       <c r="G69">
-        <v>451.46</v>
+        <v>355.17</v>
       </c>
       <c r="H69">
-        <v>355.17</v>
+        <v>326.65</v>
       </c>
       <c r="I69">
-        <v>326.65</v>
+        <v>533.29</v>
       </c>
       <c r="J69">
-        <v>533.29</v>
+        <v>336.21</v>
       </c>
       <c r="K69">
-        <v>336.21</v>
+        <v>298.9</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
@@ -5519,34 +5519,34 @@
         <v>74</v>
       </c>
       <c r="B70">
-        <v>512675330.0</v>
+        <v>512682730.0</v>
       </c>
       <c r="C70">
-        <v>512682730.0</v>
+        <v>507810330.0</v>
       </c>
       <c r="D70">
-        <v>507810330.0</v>
+        <v>507978280.0</v>
       </c>
       <c r="E70">
-        <v>507978280.0</v>
+        <v>508123780.0</v>
       </c>
       <c r="F70">
-        <v>508123780.0</v>
+        <v>508153380.0</v>
       </c>
       <c r="G70">
-        <v>508153380.0</v>
+        <v>508288415.0</v>
       </c>
       <c r="H70">
-        <v>508288415.0</v>
+        <v>508314240.0</v>
       </c>
       <c r="I70">
-        <v>508314240.0</v>
+        <v>508609340.0</v>
       </c>
       <c r="J70">
-        <v>508609340.0</v>
+        <v>508648755.0</v>
       </c>
       <c r="K70">
-        <v>508648755.0</v>
+        <v>1017766288.0</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
@@ -5617,34 +5617,34 @@
         <v>38</v>
       </c>
       <c r="B81" s="16">
-        <v>42460.0</v>
+        <v>42825.0</v>
       </c>
       <c r="C81" s="16">
-        <v>42825.0</v>
+        <v>43190.0</v>
       </c>
       <c r="D81" s="16">
-        <v>43190.0</v>
+        <v>43555.0</v>
       </c>
       <c r="E81" s="16">
-        <v>43555.0</v>
+        <v>43921.0</v>
       </c>
       <c r="F81" s="16">
-        <v>43921.0</v>
+        <v>44286.0</v>
       </c>
       <c r="G81" s="16">
-        <v>44286.0</v>
+        <v>44651.0</v>
       </c>
       <c r="H81" s="16">
-        <v>44651.0</v>
+        <v>45016.0</v>
       </c>
       <c r="I81" s="16">
-        <v>45016.0</v>
+        <v>45382.0</v>
       </c>
       <c r="J81" s="16">
-        <v>45382.0</v>
+        <v>45747.0</v>
       </c>
       <c r="K81" s="16">
-        <v>45747.0</v>
+        <v>46112.0</v>
       </c>
     </row>
     <row r="82" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5652,34 +5652,34 @@
         <v>32</v>
       </c>
       <c r="B82">
-        <v>907.47</v>
+        <v>793.75</v>
       </c>
       <c r="C82">
-        <v>793.75</v>
+        <v>796.43</v>
       </c>
       <c r="D82">
-        <v>796.43</v>
+        <v>844.78</v>
       </c>
       <c r="E82">
-        <v>844.78</v>
+        <v>1279.55</v>
       </c>
       <c r="F82">
-        <v>1279.55</v>
+        <v>1392.13</v>
       </c>
       <c r="G82">
-        <v>1392.13</v>
+        <v>955.37</v>
       </c>
       <c r="H82">
-        <v>955.37</v>
+        <v>1557.57</v>
       </c>
       <c r="I82">
-        <v>1557.57</v>
+        <v>2724.03</v>
       </c>
       <c r="J82">
-        <v>2724.03</v>
+        <v>2286.63</v>
       </c>
       <c r="K82">
-        <v>2286.63</v>
+        <v>2828.45</v>
       </c>
     </row>
     <row r="83" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -5687,34 +5687,34 @@
         <v>33</v>
       </c>
       <c r="B83">
-        <v>-491.14</v>
+        <v>-878.97</v>
       </c>
       <c r="C83">
-        <v>-878.97</v>
+        <v>39.26</v>
       </c>
       <c r="D83">
-        <v>39.26</v>
+        <v>-513.14</v>
       </c>
       <c r="E83">
-        <v>-513.14</v>
+        <v>102.94</v>
       </c>
       <c r="F83">
-        <v>102.94</v>
+        <v>-1687.89</v>
       </c>
       <c r="G83">
-        <v>-1687.89</v>
+        <v>-558.14</v>
       </c>
       <c r="H83">
-        <v>-558.14</v>
+        <v>-898.95</v>
       </c>
       <c r="I83">
-        <v>-898.95</v>
+        <v>-1769.29</v>
       </c>
       <c r="J83">
-        <v>-1769.29</v>
+        <v>-1541.59</v>
       </c>
       <c r="K83">
-        <v>-1541.59</v>
+        <v>-1224.1</v>
       </c>
     </row>
     <row r="84" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -5722,34 +5722,34 @@
         <v>34</v>
       </c>
       <c r="B84">
-        <v>-371.06</v>
+        <v>40.66</v>
       </c>
       <c r="C84">
-        <v>40.66</v>
+        <v>-789.75</v>
       </c>
       <c r="D84">
-        <v>-789.75</v>
+        <v>-360.56</v>
       </c>
       <c r="E84">
-        <v>-360.56</v>
+        <v>-849.21</v>
       </c>
       <c r="F84">
-        <v>-849.21</v>
+        <v>-76.24</v>
       </c>
       <c r="G84">
-        <v>-76.24</v>
+        <v>-467.96</v>
       </c>
       <c r="H84">
-        <v>-467.96</v>
+        <v>-656.43</v>
       </c>
       <c r="I84">
-        <v>-656.43</v>
+        <v>-742.45</v>
       </c>
       <c r="J84">
-        <v>-742.45</v>
+        <v>-917.94</v>
       </c>
       <c r="K84">
-        <v>-917.94</v>
+        <v>-1672.77</v>
       </c>
     </row>
     <row r="85" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5757,34 +5757,34 @@
         <v>35</v>
       </c>
       <c r="B85">
-        <v>45.27</v>
+        <v>-44.56</v>
       </c>
       <c r="C85">
-        <v>-44.56</v>
+        <v>45.94</v>
       </c>
       <c r="D85">
-        <v>45.94</v>
+        <v>-28.92</v>
       </c>
       <c r="E85">
-        <v>-28.92</v>
+        <v>533.28</v>
       </c>
       <c r="F85">
-        <v>533.28</v>
+        <v>-372.0</v>
       </c>
       <c r="G85">
-        <v>-372.0</v>
+        <v>-70.73</v>
       </c>
       <c r="H85">
-        <v>-70.73</v>
+        <v>2.19</v>
       </c>
       <c r="I85">
-        <v>2.19</v>
+        <v>212.29</v>
       </c>
       <c r="J85">
-        <v>212.29</v>
+        <v>-172.9</v>
       </c>
       <c r="K85">
-        <v>-172.9</v>
+        <v>-68.42</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
@@ -5804,34 +5804,34 @@
         <v>77</v>
       </c>
       <c r="B90">
-        <v>294.65</v>
+        <v>349.58</v>
       </c>
       <c r="C90">
-        <v>349.58</v>
+        <v>458.9</v>
       </c>
       <c r="D90">
-        <v>458.9</v>
+        <v>623.13</v>
       </c>
       <c r="E90">
-        <v>623.13</v>
+        <v>678.2</v>
       </c>
       <c r="F90">
-        <v>678.2</v>
+        <v>904.7</v>
       </c>
       <c r="G90">
-        <v>904.7</v>
+        <v>1227.15</v>
       </c>
       <c r="H90">
-        <v>1227.15</v>
+        <v>1176.5</v>
       </c>
       <c r="I90">
-        <v>1176.5</v>
+        <v>1507.35</v>
       </c>
       <c r="J90">
-        <v>1507.35</v>
+        <v>1424.65</v>
       </c>
       <c r="K90">
-        <v>1424.65</v>
+        <v>1285.0</v>
       </c>
     </row>
     <row r="92" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -5847,31 +5847,31 @@
         <v>102.54</v>
       </c>
       <c r="C93" s="31">
-        <v>102.54</v>
+        <v>101.56</v>
       </c>
       <c r="D93" s="31">
-        <v>101.56</v>
+        <v>101.6</v>
       </c>
       <c r="E93" s="31">
-        <v>101.6</v>
+        <v>101.62</v>
       </c>
       <c r="F93" s="31">
-        <v>101.62</v>
+        <v>101.63</v>
       </c>
       <c r="G93" s="31">
-        <v>101.63</v>
+        <v>101.66</v>
       </c>
       <c r="H93" s="31">
         <v>101.66</v>
       </c>
       <c r="I93" s="31">
-        <v>101.66</v>
+        <v>101.72</v>
       </c>
       <c r="J93" s="31">
-        <v>101.72</v>
+        <v>101.73</v>
       </c>
       <c r="K93" s="31">
-        <v>101.73</v>
+        <v>101.78</v>
       </c>
     </row>
   </sheetData>
